--- a/data/trans_orig/P70B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023</t>
+          <t>Población según como se adapta su horario laboral a sus compromisos sociales y familiares fuera del trabajo en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1836</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>23935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>119600</t>
+          <t>120022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148438</t>
+          <t>149364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87555</t>
+          <t>88405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107259</t>
+          <t>106815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216636</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251795</t>
+          <t>250379</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>37568</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64245</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31101</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73375</t>
+          <t>74328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108414</t>
+          <t>106559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39914</t>
+          <t>40467</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79112</t>
+          <t>78524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72307</t>
+          <t>74885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115390</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129005</t>
+          <t>130613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171270</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96661</t>
+          <t>95996</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120122</t>
+          <t>118638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>234408</t>
+          <t>235863</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280911</t>
+          <t>280395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46347</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65866</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24348</t>
+          <t>23372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43822</t>
+          <t>45888</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>18339</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46780</t>
+          <t>45770</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>73035</t>
+          <t>70746</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>52503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79144</t>
+          <t>78694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44784</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64064</t>
+          <t>63329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103804</t>
+          <t>105121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135819</t>
+          <t>135547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28700</t>
+          <t>29203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50024</t>
+          <t>50905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44303</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90903</t>
+          <t>89196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>34425</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61309</t>
+          <t>60990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38954</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69466</t>
+          <t>71256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41251</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>162285</t>
+          <t>158492</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96830</t>
+          <t>92583</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>224211</t>
+          <t>217378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>65847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99865</t>
+          <t>100121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61019</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195508</t>
+          <t>206261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>144284</t>
+          <t>146188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>293544</t>
+          <t>304454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,62 +3041,62 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>3203</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70932</t>
+          <t>72346</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88428</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>64451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79154</t>
+          <t>78675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>142107</t>
+          <t>139636</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163153</t>
+          <t>163218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>35894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25190</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39799</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>49634</t>
+          <t>49762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>71187</t>
+          <t>71170</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41387</t>
+          <t>40616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>60455</t>
+          <t>62125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>67147</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>88286</t>
+          <t>88847</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>37001</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52845</t>
+          <t>52131</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>108557</t>
+          <t>108884</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>134913</t>
+          <t>136824</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11585</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>27051</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29288</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>48890</t>
+          <t>48588</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26112</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>51792</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>54126</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>85377</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>118085</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>163251</t>
+          <t>164455</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>123186</t>
+          <t>125983</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>153652</t>
+          <t>155003</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>252829</t>
+          <t>252380</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>306768</t>
+          <t>304774</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>126391</t>
+          <t>126508</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>169743</t>
+          <t>168651</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>117025</t>
+          <t>117664</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>147937</t>
+          <t>146580</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>253583</t>
+          <t>255517</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>305767</t>
+          <t>306498</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>912</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>32985</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>40983</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>40376</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77798</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>511559</t>
+          <t>513801</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>606997</t>
+          <t>603481</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>196778</t>
+          <t>198111</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>227318</t>
+          <t>227363</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>722693</t>
+          <t>725891</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>843816</t>
+          <t>845095</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>70191</t>
+          <t>70395</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12369</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27030</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>85647</t>
+          <t>85218</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>27930</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>64621</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26720</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>62709</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>142719</t>
+          <t>138148</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>259661</t>
+          <t>261414</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>141400</t>
+          <t>139382</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>195911</t>
+          <t>195893</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>298039</t>
+          <t>301128</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>433254</t>
+          <t>433433</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1151413</t>
+          <t>1149872</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1485142</t>
+          <t>1541874</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>718174</t>
+          <t>692169</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>899564</t>
+          <t>901657</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1966278</t>
+          <t>1955952</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2344802</t>
+          <t>2380011</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,48%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>300865</t>
+          <t>276008</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>515387</t>
+          <t>512482</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>355791</t>
+          <t>357222</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>568702</t>
+          <t>594142</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>698987</t>
+          <t>686233</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>997183</t>
+          <t>1003424</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70B_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70B_2023-Provincia-trans_orig.xlsx
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>27024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136172</t>
+          <t>139225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>120022</t>
+          <t>125375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149364</t>
+          <t>151529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98394</t>
+          <t>106257</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>88405</t>
+          <t>97457</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106815</t>
+          <t>115899</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>234566</t>
+          <t>245482</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216916</t>
+          <t>228094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250379</t>
+          <t>260421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50681</t>
+          <t>53002</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>40998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>65712</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>39306</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>90197</t>
+          <t>92308</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74328</t>
+          <t>78247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106559</t>
+          <t>109180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>202305</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>355062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12724</t>
+          <t>14369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
+          <t>56049</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78524</t>
+          <t>74573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25315</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91325</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74885</t>
+          <t>71829</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115085</t>
+          <t>113863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>150244</t>
+          <t>160011</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130613</t>
+          <t>140082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168988</t>
+          <t>180383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>108488</t>
+          <t>114132</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95996</t>
+          <t>102390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118638</t>
+          <t>126280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>258731</t>
+          <t>274142</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>235863</t>
+          <t>252371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280395</t>
+          <t>296124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30331</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>53095</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36457</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67371</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>167092</t>
+          <t>175989</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167092</t>
+          <t>175989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>167092</t>
+          <t>175989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>406702</t>
+          <t>425477</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>406702</t>
+          <t>425477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>406702</t>
+          <t>425477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,22 +1863,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16608</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9587</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18339</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>58867</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45770</t>
+          <t>46750</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>67019</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52503</t>
+          <t>55900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78694</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>46391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63329</t>
+          <t>65939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>122734</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105121</t>
+          <t>108985</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135547</t>
+          <t>139030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>39549</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29203</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50905</t>
+          <t>50904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>75413</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>89196</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>32783</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21585</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>17565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>44094</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18460</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34425</t>
+          <t>42586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>16347</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37821</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>30642</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60990</t>
+          <t>65102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52913</t>
+          <t>65120</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38870</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>71256</t>
+          <t>85010</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>106839</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>72281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>158492</t>
+          <t>97821</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>159751</t>
+          <t>151106</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92583</t>
+          <t>130348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>217378</t>
+          <t>176308</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83783</t>
+          <t>105453</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65847</t>
+          <t>84387</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100121</t>
+          <t>127281</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>121121</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206261</t>
+          <t>72960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>204904</t>
+          <t>164822</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146188</t>
+          <t>143675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>304454</t>
+          <t>188086</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>210996</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>210996</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>168497</t>
+          <t>210996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>257774</t>
+          <t>179263</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>257774</t>
+          <t>179263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257774</t>
+          <t>179263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>426270</t>
+          <t>390258</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>426270</t>
+          <t>390258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>426270</t>
+          <t>390258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>649</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>649</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>8798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>80701</t>
+          <t>98040</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72346</t>
+          <t>89289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88064</t>
+          <t>107170</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>72135</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>64451</t>
+          <t>71751</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78675</t>
+          <t>88366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>152836</t>
+          <t>178875</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139636</t>
+          <t>166551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>163218</t>
+          <t>189407</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>31437</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25584</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>56435</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>71170</t>
+          <t>79574</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>135423</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>254865</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>254865</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>220673</t>
+          <t>254865</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>31933</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22184</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40616</t>
+          <t>40970</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25412</t>
+          <t>24117</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>48572</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>39555</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>62125</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>78497</t>
+          <t>78379</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66395</t>
+          <t>68511</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>88847</t>
+          <t>89545</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>44520</t>
+          <t>45600</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>37583</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52131</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>123018</t>
+          <t>123979</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>108884</t>
+          <t>108621</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>136824</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>18461</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>26702</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>38905</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29749</t>
+          <t>30549</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>48588</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>12230</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>30261</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>41198</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26590</t>
+          <t>28640</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>52047</t>
+          <t>57537</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>30294</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>39100</t>
+          <t>47170</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>76919</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>54126</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>87029</t>
+          <t>94625</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>154994</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>120665</t>
+          <t>134224</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>164455</t>
+          <t>177155</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>138369</t>
+          <t>163253</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>125983</t>
+          <t>146984</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>155003</t>
+          <t>181736</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>278315</t>
+          <t>318247</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>252380</t>
+          <t>290883</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>304774</t>
+          <t>345521</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>147240</t>
+          <t>179635</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>126508</t>
+          <t>157581</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>168651</t>
+          <t>202334</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>132488</t>
+          <t>156753</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>117664</t>
+          <t>139873</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>146580</t>
+          <t>173813</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>279728</t>
+          <t>336388</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>255517</t>
+          <t>306111</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>306498</t>
+          <t>366590</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>335486</t>
+          <t>388726</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306370</t>
+          <t>362304</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306370</t>
+          <t>362304</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306370</t>
+          <t>362304</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>641855</t>
+          <t>751030</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>641855</t>
+          <t>751030</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>641855</t>
+          <t>751030</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10540</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>32985</t>
+          <t>14120</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>25555</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>15458</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40983</t>
+          <t>37125</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>30007</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>45931</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>52843</t>
+          <t>60422</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>46620</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>77942</t>
+          <t>75810</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>562936</t>
+          <t>379905</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>513801</t>
+          <t>361373</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>603481</t>
+          <t>395715</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>215991</t>
+          <t>253879</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>198111</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>227363</t>
+          <t>266510</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>778928</t>
+          <t>633785</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>725891</t>
+          <t>611562</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>845095</t>
+          <t>654050</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>32992</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>70395</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>31315</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>25987</t>
+          <t>51238</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>85218</t>
+          <t>84118</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>272011</t>
+          <t>313144</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>900336</t>
+          <t>768080</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>46258</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>62642</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>35108</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>45610</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>88572</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>110924</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5390,102 +5390,102 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>226746</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>138148</t>
+          <t>193173</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>261414</t>
+          <t>260955</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>183037</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>161238</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>207654</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>12,1%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>409783</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>373013</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>450079</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>167782</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>139382</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>195893</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>380657</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>433433</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1267240</t>
+          <t>1142692</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1149872</t>
+          <t>1090903</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1541874</t>
+          <t>1185697</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>838722</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>692169</t>
+          <t>869067</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>901657</t>
+          <t>938821</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>2105962</t>
+          <t>2048350</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1955952</t>
+          <t>1986938</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2380011</t>
+          <t>2109219</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>437044</t>
+          <t>504666</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>466686</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>512482</t>
+          <t>552089</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>418948</t>
+          <t>389479</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>357222</t>
+          <t>357676</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>594142</t>
+          <t>417242</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>855992</t>
+          <t>894145</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>686233</t>
+          <t>842349</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1003424</t>
+          <t>952063</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1963416</t>
+          <t>1927568</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1461961</t>
+          <t>1513282</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3425377</t>
+          <t>3440851</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
